--- a/src/attributions/attributions_ig_traj_46.xlsx
+++ b/src/attributions/attributions_ig_traj_46.xlsx
@@ -1002,25 +1002,25 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.125240297346129</v>
+        <v>-0.1591338017565369</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.02163575507697109</v>
+        <v>0.001651909559972236</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4184214014596861</v>
+        <v>0.1411082376947908</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -1029,7 +1029,7 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0612093427335972</v>
+        <v>0.1530262662213319</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
@@ -1038,25 +1038,25 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.004950386890326439</v>
+        <v>0.004780341746455529</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05878046751331522</v>
+        <v>0.02086668569807311</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02216997293115552</v>
+        <v>-0.02320553314803209</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,37 +1065,37 @@
         <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02125249120810159</v>
+        <v>0.1550807338728095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.03933253532318837</v>
+        <v>0.04903452171011132</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1564723212020225</v>
+        <v>-0.03665184382790825</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.08026828373159288</v>
+        <v>0.08353965512260239</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.06019922573563489</v>
+        <v>0.004132343925011329</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1104,40 +1104,40 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04512062873349177</v>
+        <v>-0.09852496475142415</v>
       </c>
       <c r="AM2" t="n">
         <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.06851142214200037</v>
+        <v>-0.1314305247329573</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.03268902929002054</v>
+        <v>0.01270247214051591</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.186901514118349</v>
+        <v>-0.2125508625734027</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,25 +1146,25 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2065004335995192</v>
+        <v>0.1683791712592622</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.6887664520505286</v>
+        <v>0.08211543145298543</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
         <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01894009352939086</v>
+        <v>-0.03376703268089918</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,13 +1173,13 @@
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.006441516562333868</v>
+        <v>-0.02675940334606179</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.01206215010767269</v>
+        <v>0.004638821495646635</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.1033191181922315</v>
+        <v>0.0888368764790002</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
@@ -1200,133 +1200,133 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.02689803731296748</v>
+        <v>-0.06337173571796594</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.06880979230979786</v>
+        <v>-0.05471710154228338</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.03640006562183386</v>
+        <v>-0.2074062069846493</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.1041602445250437</v>
+        <v>0.0454638817281348</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.3533989387872934</v>
+        <v>0.1375065828316337</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.05718324837793003</v>
+        <v>0.1462439744302907</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.004071770007832734</v>
+        <v>0.005308189335778635</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.1368273578472763</v>
+        <v>-0.1217553084756337</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.02059730504935625</v>
+        <v>0.1459153668331201</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.2366059215347191</v>
+        <v>0.03662439850846883</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.06926949174031549</v>
+        <v>-0.04974280932406926</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.05544577776608981</v>
+        <v>0.1351927332882803</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.00906677743070684</v>
+        <v>-0.03692046364480794</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.1795644398961981</v>
+        <v>-0.1247490289927966</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.01419227219198558</v>
+        <v>0.001041997106907547</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,25 +1335,25 @@
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.1425396558533236</v>
+        <v>0.06999869245729137</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.006239345371230459</v>
+        <v>-0.001481883839451606</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.008156669826626713</v>
+        <v>0.1476145713692398</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.02551923384293512</v>
+        <v>0.01192202400216735</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.0002323447000390321</v>
+        <v>-0.04985260036475053</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
@@ -1380,73 +1380,73 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.06621575665718482</v>
+        <v>0.02018514456342079</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.0364427187409566</v>
+        <v>-0.0508346437976027</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.1734881142207791</v>
+        <v>-0.1051413007961077</v>
       </c>
       <c r="EC2" t="n">
         <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01522877706773663</v>
+        <v>0.04179342961327477</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>-0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01902909637924046</v>
+        <v>-0.0001815398028135916</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.1332960166983007</v>
+        <v>-0.1171937427956036</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.1369094504949818</v>
+        <v>0.09592770007930364</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.01801057295006164</v>
+        <v>0.02363781727394533</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.0003412554401219732</v>
+        <v>0.07463096660711209</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
@@ -1455,25 +1455,25 @@
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.05639603061976282</v>
+        <v>0.1338561791331894</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.02337382119963191</v>
+        <v>0.001785016639052328</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.1438511798448767</v>
+        <v>-0.1083644267485324</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1488,34 +1488,34 @@
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.04385328042967794</v>
+        <v>0.07717261504708436</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.007768024014138827</v>
+        <v>-0.1068875468555268</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0.09051989066439345</v>
+        <v>-0.004544661330517456</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.09689723322376907</v>
+        <v>0.06810430865019927</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,40 +1524,40 @@
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.0327114138055624</v>
+        <v>0.07561257090333756</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.3164465101848297</v>
+        <v>-0.06499120978022088</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.08617096190707757</v>
+        <v>0.08195639086569186</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
         <v>0</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.01026850319250149</v>
+        <v>0.07637061591143371</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1571,22 +1571,22 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.07737532448959634</v>
+        <v>-0.09038791732261439</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.04201405436497842</v>
+        <v>0.01720823867001999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4131055637972508</v>
+        <v>0.14586587448668</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.04827676874553109</v>
+        <v>0.1288457560555435</v>
       </c>
       <c r="L3" t="n">
         <v>-0</v>
@@ -1607,13 +1607,13 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0006468334888985035</v>
+        <v>0.01683627945316208</v>
       </c>
       <c r="O3" t="n">
-        <v>0.109565856242702</v>
+        <v>0.03382098129506367</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05744342173441253</v>
+        <v>-0.05036715820525018</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09297109730118731</v>
+        <v>0.03223651027733947</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1790222829896884</v>
+        <v>0.07093503282663527</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.09264195907093067</v>
+        <v>-0.03842633207119917</v>
       </c>
       <c r="AD3" t="n">
         <v>-0</v>
@@ -1661,43 +1661,43 @@
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02074700509909452</v>
+        <v>-0.06731770403694386</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.05050587966543744</v>
+        <v>-0.05188220410186155</v>
       </c>
       <c r="AH3" t="n">
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.02508640864006878</v>
+        <v>-0.0907795247548553</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.07330404234104788</v>
+        <v>-0.1044546238888957</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.151860566934404</v>
+        <v>0.03722275363630047</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
@@ -1706,25 +1706,25 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1784178426422713</v>
+        <v>-0.1987742227718205</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1815971428003996</v>
+        <v>-0.01474381437995731</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.4971056792853301</v>
+        <v>0.2217312497929911</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
@@ -1733,7 +1733,7 @@
         <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.07501867382382393</v>
+        <v>0.01471255374837012</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
@@ -1742,16 +1742,16 @@
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02063091858849369</v>
+        <v>0.007673203905570448</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.03610326724771048</v>
+        <v>0.0185699744813202</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1760,46 +1760,46 @@
         <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1590105516288536</v>
+        <v>0.07205341861253316</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1055539061624547</v>
+        <v>-0.03366557255809181</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.0925076657857546</v>
+        <v>-0.01397226664805877</v>
       </c>
       <c r="BR3" t="n">
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.06090373492439716</v>
+        <v>-0.1447867885693379</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1886189919756815</v>
+        <v>0.01546617612426731</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2533434524317164</v>
+        <v>0.1715528923537128</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
@@ -1808,52 +1808,52 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0613494391373363</v>
+        <v>0.1810057307980093</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.006403330561024899</v>
+        <v>0.0042653897193155</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.1441572664400116</v>
+        <v>-0.1047047604914502</v>
       </c>
       <c r="CJ3" t="n">
         <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1305411725039696</v>
+        <v>0.1367574352491406</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2132573993532633</v>
+        <v>-0.03377786266283628</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.06553213134854673</v>
+        <v>-0.182208262202061</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
@@ -1868,46 +1868,46 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.03153194278594443</v>
+        <v>0.1858265477060599</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.01939659577220347</v>
+        <v>-0.01965188233567015</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.1638385424879671</v>
+        <v>-0.1080503998373362</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0119148405021061</v>
+        <v>-0.004832345185855605</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.02642518907358262</v>
+        <v>0.005359059516223842</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.05306627222401972</v>
+        <v>-0.1046080393067687</v>
       </c>
       <c r="DK3" t="n">
         <v>-0</v>
@@ -1916,79 +1916,79 @@
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.01011775737307992</v>
+        <v>0.1165364479188878</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.02089441426787587</v>
+        <v>-0.004511677619566575</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.007182088398253523</v>
+        <v>-0.05123950328754127</v>
       </c>
       <c r="DT3" t="n">
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1287047512728499</v>
+        <v>0.104657693996797</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.03419144115372797</v>
+        <v>-0.01086390748547351</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.08784615963606593</v>
+        <v>0.1391243840903864</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.00287491912098803</v>
+        <v>0.1563246198499693</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.05956112271821268</v>
+        <v>-0.01142450066895748</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.08201552434584766</v>
+        <v>-0.03768027491578994</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.03465422380272217</v>
+        <v>-0.09001485953820845</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03088909603066646</v>
+        <v>0.004302725364587566</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.05150846234371507</v>
+        <v>-0.04097375585951887</v>
       </c>
       <c r="EU3" t="n">
         <v>-0</v>
@@ -2024,40 +2024,40 @@
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0267668778008671</v>
+        <v>0.1915522986506144</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.04608002345889464</v>
+        <v>-0.0005470242951626554</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.1500746086985797</v>
+        <v>-0.1089036697724757</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.06409009547380445</v>
+        <v>0.03992550478295436</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
@@ -2066,25 +2066,25 @@
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.01241181238057464</v>
+        <v>0.07165930618095127</v>
       </c>
       <c r="FL3" t="n">
-        <v>-0.1561883205135285</v>
+        <v>-0.02283906624570229</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1444549769442565</v>
+        <v>0.1716435817978617</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,10 +2093,10 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.08151982200902154</v>
+        <v>0.02716305390279481</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0146902689904822</v>
+        <v>0.008046072016142628</v>
       </c>
       <c r="FV3" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.05034178108269291</v>
+        <v>0.1681401845622217</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2123,13 +2123,13 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1072540513491005</v>
+        <v>-0.03958794071033206</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>-0</v>
@@ -2140,25 +2140,25 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02910508709710302</v>
+        <v>0.3633256587045675</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02719018858758708</v>
+        <v>0.05891230865376676</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02163269228189662</v>
+        <v>-0.1870638152301316</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,34 +2167,34 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004610547531083419</v>
+        <v>0.1724163764518783</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.008429574979292991</v>
+        <v>-0.0118634732170895</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002868329182419681</v>
+        <v>0.02807273474432983</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.005241455588618308</v>
+        <v>0.1749392383616207</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,37 +2203,37 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.01600470448164149</v>
+        <v>-0.1757661104174194</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01678266665590853</v>
+        <v>0.0109805905844446</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01517324685152308</v>
+        <v>-0.01632107724866924</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01117262044730659</v>
+        <v>-0.2823952623296842</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.01099134884984442</v>
+        <v>-0.03739258863142809</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,13 +2242,13 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00487695612261039</v>
+        <v>0.1057503566906129</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,37 +2257,37 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01059833957154258</v>
+        <v>0.09334422505793916</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.003896223220294401</v>
+        <v>-0.0879578132679866</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.03905056867369019</v>
+        <v>0.671167476732626</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.03917404673052311</v>
+        <v>-0.1977229822962281</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.01307948149022929</v>
+        <v>-0.2637009445794663</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2302,19 +2302,19 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.00924011178388</v>
+        <v>-0.0007774619897782122</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.006869787526253931</v>
+        <v>-0.03771769710336952</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.0049456055086821</v>
+        <v>-0.03468635152692941</v>
       </c>
       <c r="BI4" t="n">
         <v>-0</v>
@@ -2326,28 +2326,28 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02970815190337998</v>
+        <v>0.01747184545973727</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01267790523371823</v>
+        <v>0.1056487388761345</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.00518547298531445</v>
+        <v>0.146707242286805</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.01417225936244665</v>
+        <v>0.5035018208081096</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,37 +2365,37 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.02123172535752216</v>
+        <v>-0.02153516973731642</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004607409079406578</v>
+        <v>-0.157157258214447</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.003195352772099748</v>
+        <v>-0.1952166674481956</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01021053260391885</v>
+        <v>-0.04086260574468365</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01191783822372096</v>
+        <v>0.1517960739138902</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002527257226687133</v>
+        <v>-0.2677731028669956</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
@@ -2419,40 +2419,40 @@
         <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.004133818867855252</v>
+        <v>0.1707427637281959</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.002116796450177274</v>
+        <v>0.1220182054483397</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001469503369822709</v>
+        <v>-0.1846168255192719</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.009823954736655718</v>
+        <v>-0.04910525941401723</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01569354879975735</v>
+        <v>0.1455080530529011</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01108018786274812</v>
+        <v>-0.05671902119210314</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01252648145789864</v>
+        <v>-0.1146972436755552</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.0009984141758186968</v>
+        <v>0.01752658166813045</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,31 +2485,31 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.006206573797542386</v>
+        <v>-0.1017501469316677</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01659748282713291</v>
+        <v>0.01047487344751647</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.008572193394684352</v>
+        <v>0.01267358055965425</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
@@ -2518,25 +2518,25 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.01193382048173978</v>
+        <v>0.01058831174061014</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.01363156415902247</v>
+        <v>-0.0409385420333116</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.003605460695087642</v>
+        <v>0.142109525143342</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
@@ -2545,7 +2545,7 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001053355074503144</v>
+        <v>-0.05815059248956043</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,25 +2554,25 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.006599061497596774</v>
+        <v>-0.130879415799854</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01295874462756225</v>
+        <v>0.02499024171059862</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.007208696664175946</v>
+        <v>-0.07893355588799204</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
@@ -2581,25 +2581,25 @@
         <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0213652062083301</v>
+        <v>-0.2050281463306263</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.007893052765281239</v>
+        <v>0.1020062644349683</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.003852359878142634</v>
+        <v>-0.1931308299693234</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.009714600393057994</v>
+        <v>-0.08794781430133201</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01430589164085029</v>
+        <v>0.1150729865952197</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF4" t="n">
         <v>-0</v>
@@ -2626,34 +2626,34 @@
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.0134204974989969</v>
+        <v>-0.2321684304885063</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02505046305129288</v>
+        <v>0.04980461423111743</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0133901510743258</v>
+        <v>0.1599657198527782</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002055784878975518</v>
+        <v>0.04180332917867991</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
@@ -2662,25 +2662,25 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0002465593029455378</v>
+        <v>0.00439766900685555</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.01778053084848228</v>
+        <v>-0.02164400510950222</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01462665344449953</v>
+        <v>-0.07431843443725346</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001880836763509367</v>
+        <v>0.07931548076870598</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -3278,16 +3278,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.3054775925375885</v>
+        <v>0.296562982615406</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1191082795987771</v>
+        <v>-0.1215499723112573</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.05631157429709471</v>
+        <v>-0.04615068685801724</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3299,25 +3299,25 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1361613494817015</v>
+        <v>0.1926580006389432</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.002294733193266919</v>
+        <v>0.003177582602861473</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04651416039464388</v>
+        <v>-0.04263038408104365</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -3329,82 +3329,82 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1143595549848011</v>
+        <v>0.05471461186889711</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.01575117735183796</v>
+        <v>-0.05482704503630392</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02237527427974123</v>
+        <v>-0.07357065881098182</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.06519253337355251</v>
+        <v>-0.03147448331821597</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.03098705676115913</v>
+        <v>-0.09991012211817762</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.01859109739271969</v>
+        <v>-0.101501975859362</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.04543501583484815</v>
+        <v>0.1221822497666515</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.02914749447021231</v>
+        <v>-0.06026335128263153</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01823960084811424</v>
+        <v>0.05123369306063968</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3413,25 +3413,25 @@
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4263048451438904</v>
+        <v>0.3654634375500169</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.01190168392538317</v>
+        <v>-0.1301333533483591</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1743851813085681</v>
+        <v>-0.2056991820191984</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
@@ -3440,16 +3440,16 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0180580201356551</v>
+        <v>-0.02656099983379748</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.04857090971560243</v>
+        <v>-0.01600979728977397</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0906242266745247</v>
+        <v>-0.01108802299539986</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,22 +3467,22 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04354354019680103</v>
+        <v>-0.01228061532869824</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.09497399068913168</v>
+        <v>0.03633665271053961</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01951117325719453</v>
+        <v>0.06776083137444615</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,25 +3494,25 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2253816151936224</v>
+        <v>0.2603521471197286</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.002840450104177447</v>
+        <v>-0.06351579224424758</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.00301629083487002</v>
+        <v>-0.0639484558445937</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -3521,46 +3521,46 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.07325416992720549</v>
+        <v>-0.1400289331666612</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.02193371116732339</v>
+        <v>0.1173358422792469</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.02497859000654235</v>
+        <v>0.01627419423899944</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.02413739557484641</v>
+        <v>-0.1066783576378811</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1193440142098739</v>
+        <v>0.1815827435065408</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1460855368436277</v>
+        <v>0.07251715454923678</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3575,49 +3575,49 @@
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.05983150052954238</v>
+        <v>-0.1393693932488688</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.04912537492777535</v>
+        <v>0.1282499663155051</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.01998605953862091</v>
+        <v>0.02368803987247989</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04318973332071199</v>
+        <v>-0.04677917177638483</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.007636847418410534</v>
+        <v>-0.01011070433454604</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0009421275735211564</v>
+        <v>-0.01654586286844699</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
@@ -3629,25 +3629,25 @@
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.07059090152147374</v>
+        <v>-0.08579486975912963</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.04332018506972207</v>
+        <v>0.03890061895042522</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.01252491087629871</v>
+        <v>-0.05028948705590047</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3656,43 +3656,43 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.04471508747890799</v>
+        <v>0.03849728205789617</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.06160340772463341</v>
+        <v>0.05027513767958633</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01418315159675655</v>
+        <v>-0.01488737880583702</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.03293130002343954</v>
+        <v>-0.09692480914731237</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.07300733018646829</v>
+        <v>0.1151641828228271</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0004210113166899453</v>
+        <v>0.02252931780775963</v>
       </c>
       <c r="EK6" t="n">
         <v>-0</v>
@@ -3701,31 +3701,31 @@
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.05337754395756229</v>
+        <v>-0.08308508336476003</v>
       </c>
       <c r="EQ6" t="n">
         <v>0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.03542810016146103</v>
+        <v>-0.08420895412283705</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.03352166635560132</v>
+        <v>0.01254461624624505</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3737,46 +3737,46 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.06690547858157071</v>
+        <v>-0.15496483531584</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.03036157850960786</v>
+        <v>0.1270152445639395</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.03255859580208587</v>
+        <v>0.01009310919864137</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.02122799942109724</v>
+        <v>-0.06638436556937735</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.05435224605022811</v>
+        <v>0.05169288625792425</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.003926436579000847</v>
+        <v>-0.004207540589980309</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,28 +3785,28 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.006722461319961977</v>
+        <v>0.008238436596086892</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.002227462733589296</v>
+        <v>0.1412659942044857</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01448848839528436</v>
+        <v>-0.01074682566807233</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,31 +3815,31 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.007778256790860337</v>
+        <v>-0.1168057623419167</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.0204065869253393</v>
+        <v>0.06413901969914138</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05609020699536508</v>
+        <v>0.3750562671799201</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,25 +4425,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.006731553400387966</v>
+        <v>-0.003270938921614383</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02458099888582469</v>
+        <v>-0.1691312887647525</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01274479621649951</v>
+        <v>0.3068751233677499</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.009567471101721575</v>
+        <v>-0.07833230831337835</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004530174398476144</v>
+        <v>0.03024801259935011</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.003273098154125832</v>
+        <v>0.1320575312599535</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -4479,52 +4479,52 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.01266405712156691</v>
+        <v>-0.04342289166798524</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01808235221986935</v>
+        <v>0.04072542744265454</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0185036110552021</v>
+        <v>-0.008490837284558354</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02121369027051047</v>
+        <v>-0.2264193934406579</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.008743981067922364</v>
+        <v>0.04663252653485112</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01193527285555703</v>
+        <v>0.1194355131273919</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -4533,16 +4533,16 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.003757988168317749</v>
+        <v>0.02234351964674106</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.00660101154664889</v>
+        <v>-0.07487423302540194</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -4551,19 +4551,19 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.06479596608286443</v>
+        <v>0.5313832405649128</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01036925531285347</v>
+        <v>-0.2555774822632096</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.01404454909819755</v>
+        <v>-0.240812340153976</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,40 +4572,40 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01578535774238352</v>
+        <v>-0.006582762710391887</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.007241418936256764</v>
+        <v>-0.06702706555639101</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.004172330960384291</v>
+        <v>-0.0282481154905312</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03340112276164187</v>
+        <v>0.01523058960409389</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,13 +4614,13 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01746098336305166</v>
+        <v>0.1222367891382063</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01102426060729082</v>
+        <v>0.07856581918425666</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
@@ -4629,28 +4629,28 @@
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02552016778466155</v>
+        <v>0.3645368836754715</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.02297448037174917</v>
+        <v>-0.02121945827647664</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01895051740498904</v>
+        <v>-0.08855168641147111</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
@@ -4659,22 +4659,22 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.001136988507668813</v>
+        <v>-0.1572562774490451</v>
       </c>
       <c r="CF8" t="n">
         <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.003489453634461972</v>
+        <v>0.01638082860861711</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.01490556899625802</v>
+        <v>0.1075040628216449</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4683,52 +4683,52 @@
         <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01028061799712751</v>
+        <v>-0.2019825647711698</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00569572748687843</v>
+        <v>0.2673071062270286</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.03027942288783964</v>
+        <v>0.02547696053891644</v>
       </c>
       <c r="CS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0007788391321184633</v>
+        <v>-0.1435330409726893</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.003180062225933485</v>
+        <v>0.0221765514519914</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01803994101648909</v>
+        <v>0.116886847382297</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4737,52 +4737,52 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.0001501543065914756</v>
+        <v>-0.1023655803897843</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01680371776748153</v>
+        <v>-0.1016218885881402</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01347147892813701</v>
+        <v>0.1149043631848453</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0005757055970128839</v>
+        <v>-0.1213180370440733</v>
       </c>
       <c r="DP8" t="n">
         <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0176099172881384</v>
+        <v>-0.01575012498922523</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.004516474496740992</v>
+        <v>0.02200610768545759</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
         <v>-0</v>
@@ -4794,25 +4794,25 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.02246882419558841</v>
+        <v>0.01853188698578601</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03034961973217785</v>
+        <v>-0.08594611226987579</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01490270081254944</v>
+        <v>0.05711985497502418</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,76 +4821,76 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0003380305499751253</v>
+        <v>-0.03360768838114778</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.004110566419791475</v>
+        <v>-0.03399808230436228</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.006637382295388534</v>
+        <v>0.03266047218606471</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.008290549833578376</v>
+        <v>-0.07487560690978716</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02479712136755212</v>
+        <v>-0.1848083094946574</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.03992440018511622</v>
+        <v>-0.1463852549081761</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.004451702128262331</v>
+        <v>-0.1689649639517236</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.004384769836463702</v>
+        <v>0.003762317363812411</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.01923683641701364</v>
+        <v>0.09502887110410443</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4902,34 +4902,34 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02083282581496017</v>
+        <v>-0.1326995017607324</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.0310523341654663</v>
+        <v>0.131662043911962</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.005430095008258794</v>
+        <v>0.09121824673850962</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.005566260741981514</v>
+        <v>0.01434288178752227</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
@@ -4938,25 +4938,25 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.007680765987871807</v>
+        <v>-0.0437588674644841</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.03130618010069067</v>
+        <v>-0.08554235885197096</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.01263648518408482</v>
+        <v>-0.07236079045810337</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
@@ -4968,13 +4968,13 @@
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.006786083501373907</v>
+        <v>0.03272138234842568</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.383560706142668</v>
+        <v>0.4195398635701382</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09779076190886185</v>
+        <v>-0.1940622196115255</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1062480879181889</v>
+        <v>-0.1029567643891346</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,25 +5006,25 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2025081759917834</v>
+        <v>0.3071124412401102</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.02344589105414722</v>
+        <v>-0.06887104834230036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09216220952725029</v>
+        <v>-0.1211770201854508</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1005875586742831</v>
+        <v>0.09402770621750255</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003118447783553456</v>
+        <v>-0.06202443986806605</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01680217638999137</v>
+        <v>-0.09544363655562305</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.08088540882238177</v>
+        <v>-0.05152267965002895</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.03509322919636021</v>
+        <v>-0.06738113774570222</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02734683607182281</v>
+        <v>-0.1206220523410288</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04950817015017756</v>
+        <v>0.1611959952068814</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03048233692859553</v>
+        <v>-0.0710915833076248</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04663482393539276</v>
+        <v>0.047253251417878</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,16 +5120,16 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.411187046977498</v>
+        <v>0.4408124831387149</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.02477209548057862</v>
+        <v>-0.2000349557317669</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1038119313543385</v>
+        <v>-0.2949626250443685</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
@@ -5138,7 +5138,7 @@
         <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03242873186316206</v>
+        <v>-0.06289233951270734</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.02430949363568836</v>
+        <v>0.0007823661887627477</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1301334062255229</v>
+        <v>-0.02659712596666776</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05337060940467452</v>
+        <v>0.007292685061807401</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.093033764246901</v>
+        <v>0.0574991120027159</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.04711800143635538</v>
+        <v>0.05993738608609366</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,25 +5201,25 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2162459638265495</v>
+        <v>0.3465828070610165</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.01159496044515772</v>
+        <v>-0.1818349849681313</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.007687215732191862</v>
+        <v>-0.1145382901186857</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -5228,46 +5228,46 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08634950662384012</v>
+        <v>-0.1537838081142594</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01632862301165547</v>
+        <v>0.1600865257655324</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.004734716443514178</v>
+        <v>0.02461548787045875</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.02071077846781871</v>
+        <v>-0.09799267904348433</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.07598249753069096</v>
+        <v>0.2086454432381451</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1295632325905316</v>
+        <v>0.1137422027845533</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,55 +5276,55 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.07007101572090073</v>
+        <v>-0.1509927691800886</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0443412138974941</v>
+        <v>0.1811062859363632</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.007757530229774965</v>
+        <v>0.03777184550538275</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.06349524954362808</v>
+        <v>-0.15595849567354</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.05466580901164889</v>
+        <v>0.0986425227679007</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.0114048404187319</v>
+        <v>-0.0635801906971797</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.04451831962517847</v>
+        <v>-0.09630824152106132</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05078749537672097</v>
+        <v>0.06324089517421669</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01403833343550674</v>
+        <v>-0.03230940821330522</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.04348691911394763</v>
+        <v>0.0353897130571518</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01530190722358319</v>
+        <v>0.05684030484815548</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.0103601159932597</v>
+        <v>-0.01700925619826033</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,16 +5390,16 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0487483369736842</v>
+        <v>-0.09534572803638158</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0693458095145932</v>
+        <v>0.1566389427016347</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03615777715312883</v>
+        <v>0.011966953256963</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
@@ -5408,7 +5408,7 @@
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.06925133461797001</v>
+        <v>-0.1151186296574244</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06869424207499901</v>
+        <v>-0.1392833366113297</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02575295877904916</v>
+        <v>0.02501044786895775</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,43 +5444,43 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08087613418741739</v>
+        <v>-0.1704104966387833</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03563388092658488</v>
+        <v>0.1757773614756193</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.01809162947725996</v>
+        <v>0.02165344206930616</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.006142198269857908</v>
+        <v>-0.06446780534880235</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04810495210678239</v>
+        <v>0.06194370740031976</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.005162947826171308</v>
+        <v>-0.007755045455501001</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
@@ -5492,28 +5492,28 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.01634764149349967</v>
+        <v>0.005152877472894031</v>
       </c>
       <c r="FR9" t="n">
         <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.01258973972723725</v>
+        <v>0.1724920715826537</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.05020980878519361</v>
+        <v>-0.01428877887000896</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,31 +5522,31 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.006822307585686176</v>
+        <v>-0.1225623561123131</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.01629035226653801</v>
+        <v>0.101103009858832</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6120,46 +6120,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2394487363606619</v>
+        <v>0.1206764815640634</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.02427804863629346</v>
+        <v>-0.02860861777684065</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04359335730758559</v>
+        <v>-0.04225200062637598</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1034008113000108</v>
+        <v>0.1001613247406415</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0006774987288295303</v>
+        <v>0.0009694847920433173</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.03972869078679241</v>
+        <v>-0.04505405681142892</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -6171,25 +6171,25 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04393748709792517</v>
+        <v>0.03253832810161995</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.01640213388346165</v>
+        <v>-0.004147660315334472</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03716836833935172</v>
+        <v>-0.000782064382986249</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6198,49 +6198,49 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04599187026902475</v>
+        <v>-0.01600451088628789</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.002716775718179981</v>
+        <v>-0.06168811628440592</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0002398457050541557</v>
+        <v>-0.06975835429413629</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.01259249517925863</v>
+        <v>0.03888896664390135</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.0122606295407652</v>
+        <v>-0.004079564933826339</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.03007417396625421</v>
+        <v>0.03559693158013447</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,43 +6258,43 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2583109022257615</v>
+        <v>0.1467133328589827</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.02945276465172876</v>
+        <v>-0.003009489259080723</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.05691293211287889</v>
+        <v>-0.07970718188416878</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03839292617255124</v>
+        <v>-0.03395186884942825</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.04339649981475312</v>
+        <v>-0.01204978664451375</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.04499530337304288</v>
+        <v>-0.01084477062248228</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,19 +6312,19 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1004711363150834</v>
+        <v>0.02926596689426552</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.01623420546759293</v>
+        <v>0.0190778431458467</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.08360294370760073</v>
+        <v>0.0575836629074668</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -6339,76 +6339,76 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1294351986594725</v>
+        <v>0.1217878921106221</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.02493859674584921</v>
+        <v>-0.02843390008215388</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01959054750795558</v>
+        <v>-0.01133678258394781</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.04390271302808058</v>
+        <v>-0.03959753011800671</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0.004568875289444049</v>
+        <v>0.03264368154918242</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.002185501883351689</v>
+        <v>0.02131039816874607</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.05535779582160233</v>
+        <v>-0.05258094879349149</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.03408725523941308</v>
+        <v>0.03954177994406802</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.05830329543965621</v>
+        <v>0.02364954762002863</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,19 +6417,19 @@
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02933316682763779</v>
+        <v>-0.03707096709232405</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.006065549474258491</v>
+        <v>0.03635710819791239</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0005974196383930968</v>
+        <v>0.024743058594294</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,28 +6438,28 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.009635321334690297</v>
+        <v>-0.0004045054062917774</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.04835572460228627</v>
+        <v>0.005413272162594625</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.003595618631672881</v>
+        <v>-0.005688323297106493</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>-0</v>
@@ -6468,52 +6468,52 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05993834142139291</v>
+        <v>-0.03770232568288034</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.003492957242538688</v>
+        <v>-0.02312770660132538</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.01084971455307731</v>
+        <v>-0.01658888926781023</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.0008174821677939163</v>
+        <v>0.04033484732243021</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.005017558660942205</v>
+        <v>0.01801750038048693</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.02086382434898494</v>
+        <v>-0.0511552323765094</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
         <v>0</v>
@@ -6522,22 +6522,22 @@
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02640660857914575</v>
+        <v>0.007755508918083749</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0.001485459922486264</v>
+        <v>0.02627105077865468</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.04091658762316984</v>
+        <v>0.04247813364493757</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6546,7 +6546,7 @@
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.02163756080775064</v>
+        <v>-0.0311006193897826</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.00790756612278333</v>
+        <v>0.04084231380048546</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01302015397924713</v>
+        <v>-0.002133504944359946</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,22 +6576,22 @@
         <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02803482642704527</v>
+        <v>-0.044654930088004</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-8.387832234335623e-05</v>
+        <v>0.04390008220941095</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01089699979392158</v>
+        <v>0.01297859257491428</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
@@ -6600,25 +6600,25 @@
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.01552284155236092</v>
+        <v>-0.001535403351288472</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.007694894124199496</v>
+        <v>-0.00881347780686827</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02058781069191494</v>
+        <v>-0.01768174785429841</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6627,25 +6627,25 @@
         <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.03303085630673852</v>
+        <v>0.01558456381399267</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.01421006535539592</v>
+        <v>0.04071387596447618</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01029489752183533</v>
+        <v>-0.04826952701019072</v>
       </c>
       <c r="FU11" t="n">
         <v>0</v>
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
@@ -6663,28 +6663,28 @@
         <v>-0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.00752952422976018</v>
+        <v>-0.0177648938582192</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.01603825399834916</v>
+        <v>-0.001187953705099389</v>
       </c>
       <c r="GC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
         <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,25 +6692,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1605399256007014</v>
+        <v>0.2367774300642678</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006401278091458649</v>
+        <v>-0.04746822210608318</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1129777584862777</v>
+        <v>-0.0961580751763431</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,25 +6719,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09602521437486368</v>
+        <v>0.3452997436143233</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.002746214388817704</v>
+        <v>-0.1044154532583031</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.067602311936051</v>
+        <v>-0.05937445131261171</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,46 +6746,46 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005347641587257957</v>
+        <v>0.06078284628117832</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01368941298279054</v>
+        <v>-0.04840040023758362</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.005106667552825693</v>
+        <v>-0.007668873730310912</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.02250904304675931</v>
+        <v>-0.009081594753707654</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01664153072447774</v>
+        <v>-0.1859088046264153</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.008213214468757512</v>
+        <v>-0.02677404686713838</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
@@ -6794,67 +6794,67 @@
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002050994031299848</v>
+        <v>0.04864424344955022</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.01367686387297896</v>
+        <v>0.02224161261405015</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.0248580347802393</v>
+        <v>-0.02897647641596475</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1157661655634606</v>
+        <v>0.3629268199661179</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.002728993117001525</v>
+        <v>-0.1507476684279172</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.05934038852766791</v>
+        <v>-0.07816405026804917</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05420781188733458</v>
+        <v>-0.04860938847807834</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.02108050105511207</v>
+        <v>-0.07097538804738386</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.04388466506577345</v>
+        <v>-0.04591068396272943</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.05513454981070844</v>
+        <v>0.09457091600208316</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,16 +6890,16 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.03051795212441109</v>
+        <v>0.08455870873626582</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.008257578638864657</v>
+        <v>-0.007213757186170615</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
         <v>0</v>
@@ -6908,7 +6908,7 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.05345725399923137</v>
+        <v>0.2705238613169614</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.008060293865336032</v>
+        <v>-0.04288529026698193</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.01318256896963498</v>
+        <v>-0.04359329473733133</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.03028753042299625</v>
+        <v>-0.09418651591673065</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.004167219635404441</v>
+        <v>0.03644213072430003</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.02568495419221335</v>
+        <v>0.06069839007633387</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6956,40 +6956,40 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01930011614524742</v>
+        <v>-0.2365219736119024</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.02440770132553023</v>
+        <v>0.1328763443227184</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01751607024815625</v>
+        <v>0.08871386174143883</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.01892324184590689</v>
+        <v>-0.08379711354978936</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
@@ -6998,40 +6998,40 @@
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.005227843423275001</v>
+        <v>0.01798252292989297</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.02457096592502378</v>
+        <v>0.05444788851634189</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.008400741825403733</v>
+        <v>0.01276836127741069</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.001042181085931774</v>
+        <v>-0.03427767069027318</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.003658381387433603</v>
+        <v>0.01051699775620684</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
         <v>-0</v>
@@ -7043,115 +7043,115 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02374218466696766</v>
+        <v>-0.1210386045744082</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01377858760746663</v>
+        <v>0.06055911153727561</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.006340237613521035</v>
+        <v>-0.05309947601491272</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.000863008966240615</v>
+        <v>0.034589556269018</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01235999970556514</v>
+        <v>-0.0005239927827108273</v>
       </c>
       <c r="EB12" t="n">
-        <v>-0.005672017873137616</v>
+        <v>-0.1112997690316853</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.0150112823882872</v>
+        <v>0.03581612618678985</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.005783313345189981</v>
+        <v>-0.02127373957072976</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.01645489694749085</v>
+        <v>0.03997518202394117</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.01700221674095626</v>
+        <v>-0.009374356729360078</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.003395472398401443</v>
+        <v>-0.04342790045132911</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.03652472835416433</v>
+        <v>0.05813060642777287</v>
       </c>
       <c r="EU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.02172432569562973</v>
+        <v>-0.101233987538667</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
@@ -7160,13 +7160,13 @@
         <v>0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.001725122734990073</v>
+        <v>0.01231355381630642</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.02803664918674889</v>
+        <v>0.05148313086699342</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,46 +7178,46 @@
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.0004097374204507665</v>
+        <v>-0.08518414438449852</v>
       </c>
       <c r="FI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01932107035061913</v>
+        <v>0.0438219644314771</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01439179446763309</v>
+        <v>0.04016262576363552</v>
       </c>
       <c r="FM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.00998018619863642</v>
+        <v>0.01465655550005593</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.01821284096184311</v>
+        <v>-0.0818689929547147</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.001032873764034734</v>
+        <v>0.003254232288996772</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7226,13 +7226,13 @@
         <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.02131610154347048</v>
+        <v>0.00421036133868862</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.01593156154605987</v>
+        <v>-0.018186794627104</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7258,28 +7258,28 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3340438755300984</v>
+        <v>0.2044259832215142</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09416441235929329</v>
+        <v>-0.1499949195892503</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.08111904231008162</v>
+        <v>0.1484738356381059</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7291,22 +7291,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2439510602214868</v>
+        <v>0.1816371309260741</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.09781014033832346</v>
+        <v>-0.1526096011519296</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1240392483071559</v>
+        <v>0.09082758766406233</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09713897809282546</v>
+        <v>0.04132341135331856</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.03022541789480143</v>
+        <v>-0.04202783274744683</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03176677749928347</v>
+        <v>-0.02119248831408843</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
@@ -7342,16 +7342,16 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.06360513665548304</v>
+        <v>0.04793906252760022</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.04558846543739795</v>
+        <v>0.09431720592918656</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03628686871525748</v>
+        <v>0.0404507435358564</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -7372,49 +7372,49 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.01393048296128684</v>
+        <v>0.04898644454024619</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.03360813812514041</v>
+        <v>-0.03189092672781117</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0666349040389084</v>
+        <v>0.007675756884389018</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1655788476775633</v>
+        <v>0.204548887728163</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.01560045412525943</v>
+        <v>-0.2180521754076369</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1642227990489524</v>
+        <v>0.01398593650154294</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
@@ -7423,16 +7423,16 @@
         <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.08415802079344267</v>
+        <v>-0.01027431528423423</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.02065491138110848</v>
+        <v>0.1268658770791365</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.08397722680833761</v>
+        <v>0.06754526825679824</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7447,49 +7447,49 @@
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.03824546883659527</v>
+        <v>-0.07292660958878534</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.05864867197975188</v>
+        <v>-0.1033937367677041</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1319784780534426</v>
+        <v>-0.1619231782428798</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.06562010493383454</v>
+        <v>0.115252496275339</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.02637017692956205</v>
+        <v>-0.1267793006879149</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.09752204316394178</v>
+        <v>-0.01882849556294201</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
@@ -7498,28 +7498,28 @@
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
         <v>-0</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0.07244843748921474</v>
+        <v>-0.084090576429613</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.02329392070746626</v>
+        <v>0.06870667129741444</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.004758822241223395</v>
+        <v>-0.03574906861520454</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7528,55 +7528,55 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.01749784617661943</v>
+        <v>-0.007424025835794197</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.01983367966106321</v>
+        <v>0.1555903900229161</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.124424635823879</v>
+        <v>0.009055860972084426</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS13" t="n">
         <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0.0556852036998321</v>
+        <v>-0.06065283368969369</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02373085443441363</v>
+        <v>0.06975408393842528</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02886582948563264</v>
+        <v>-0.05333585445230395</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
@@ -7585,16 +7585,16 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0.03595593492190684</v>
+        <v>-0.01377954231434291</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.03963889953411061</v>
+        <v>0.02614027214942493</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.002940690298625722</v>
+        <v>-0.02090644240544691</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
         <v>-0</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0.003922390200513025</v>
+        <v>-0.01951380227929182</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.02451794197222971</v>
+        <v>0.06329141705962626</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.1321886685058069</v>
+        <v>-0.07282662289153478</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,16 +7639,16 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.06371467190210452</v>
+        <v>0.02678921764638336</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.003426352596941492</v>
+        <v>0.04613240012478258</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06852304782435122</v>
+        <v>0.09522376747518538</v>
       </c>
       <c r="EB13" t="n">
         <v>0</v>
@@ -7663,46 +7663,46 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0.1119081560373049</v>
+        <v>-0.04468971498383655</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.04692045356474604</v>
+        <v>0.05095673586784902</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0602954127677601</v>
+        <v>0.0216778793735885</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
         <v>0</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0.007098793659395275</v>
+        <v>-0.0531158761711108</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02726167522552808</v>
+        <v>0.07199894251963973</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.02401818202475038</v>
+        <v>0.0150964887773984</v>
       </c>
       <c r="ET13" t="n">
         <v>0</v>
@@ -7711,103 +7711,103 @@
         <v>0</v>
       </c>
       <c r="EV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0.06942897416451115</v>
+        <v>-0.06762701162714008</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.03771866476456184</v>
+        <v>0.1014196266391742</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02821617680824693</v>
+        <v>-0.04026009452565392</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0.00704193741859249</v>
+        <v>-0.01823134940945335</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.008856894008899628</v>
+        <v>0.07190572377164137</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.07422186497351735</v>
+        <v>0.002997041511051565</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0.006097050541471913</v>
+        <v>0.0007384754090509363</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.006314526016534962</v>
+        <v>-0.006289059486497676</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.07116569187210106</v>
+        <v>0.1726796836335774</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX13" t="n">
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.04932868410382176</v>
+        <v>-0.03030387590176661</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.04668623404967054</v>
+        <v>0.1389079032088039</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
@@ -7830,19 +7830,19 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1826481596684845</v>
+        <v>0.4060691068627891</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.08032578134935006</v>
+        <v>-0.02354618662433754</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.06736872531833712</v>
+        <v>-0.2341676763374637</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
@@ -7857,61 +7857,61 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1116275671928374</v>
+        <v>0.488532653872989</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04754352768779612</v>
+        <v>-0.1397170476705887</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.03457818057300548</v>
+        <v>-0.126548728405686</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01933184771205974</v>
+        <v>0.06108434186059048</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.03079747761225275</v>
+        <v>-0.07547235993875218</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02889448121022397</v>
+        <v>0.008349281638255813</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.03720111347725556</v>
+        <v>0.01338584297490699</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -7920,40 +7920,40 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02555565233532337</v>
+        <v>-0.1956713072279525</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.002689175338362269</v>
+        <v>-0.04696680353165718</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.02947520652860531</v>
+        <v>0.08243517316374542</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01886626861178974</v>
+        <v>-0.0321531167467636</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.02868882975935926</v>
+        <v>-0.06345699158775629</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,91 +7962,91 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1196566491650138</v>
+        <v>0.4558884813734828</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.06333870851599262</v>
+        <v>-0.1949748227808658</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.0525529343728259</v>
+        <v>-0.1633479582898902</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.04133276380410803</v>
+        <v>0.03135632995225288</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.03363049694627965</v>
+        <v>-0.06742540389005079</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.007320072729079695</v>
+        <v>-0.07415358889139563</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.05425161671165871</v>
+        <v>0.07056729676785159</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.03093411696230106</v>
+        <v>0.09434114484018057</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.02106941754549382</v>
+        <v>0.05568389754945543</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.07167540801944061</v>
+        <v>0.2707416768468819</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.03638090549367472</v>
+        <v>-0.07281801844231212</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.008993454881275377</v>
+        <v>-0.09117609864296113</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
         <v>-0</v>
@@ -8073,7 +8073,7 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.02989385899019151</v>
+        <v>-0.1059165190650464</v>
       </c>
       <c r="CF14" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.01021494927292516</v>
+        <v>0.03608075716246708</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01933616188219326</v>
+        <v>0.08598920051560828</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,25 +8094,25 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.0002021315170799533</v>
+        <v>-0.2230589846646842</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.006881199366425569</v>
+        <v>0.17531060417505</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.02803817581634797</v>
+        <v>0.06222993581575119</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,25 +8121,25 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.02229336698430819</v>
+        <v>-0.1045691078984927</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.006184657115176152</v>
+        <v>0.006140800636230638</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0279594134279581</v>
+        <v>0.09383377204242571</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8154,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.01210890107323239</v>
+        <v>-0.02429771070690281</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.0104433278268914</v>
+        <v>-0.02079127372754791</v>
       </c>
       <c r="DJ14" t="n">
-        <v>-0.003805924586018734</v>
+        <v>0.02348599961958348</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,13 +8175,13 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.02789640592226996</v>
+        <v>-0.09137101487089133</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
@@ -8190,16 +8190,16 @@
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02880624034901601</v>
+        <v>0.01826019203318983</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0261480629616661</v>
+        <v>0.09625465888438195</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
@@ -8208,22 +8208,22 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.006299221443539146</v>
+        <v>0.03258435639705391</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.02702179783471992</v>
+        <v>-0.05956151214387194</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.01077363923906738</v>
+        <v>0.05856144337586889</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
@@ -8232,64 +8232,64 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.0161834078165294</v>
+        <v>-0.03075575835699146</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0190889435468605</v>
+        <v>-0.0529689646509407</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.008616091625739248</v>
+        <v>0.05707129980580207</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-3.32959205691918e-05</v>
+        <v>-0.03404645699181105</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.01568123658661064</v>
+        <v>-0.05331391749991487</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.0291336858628004</v>
+        <v>-0.08293603910332432</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.01813252205631794</v>
+        <v>-0.1167571723845735</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
@@ -8298,13 +8298,13 @@
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.003363616887637702</v>
+        <v>0.008073237323698803</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02792489609943506</v>
+        <v>0.07920740385161186</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.02403887670226089</v>
+        <v>-0.08074588559766334</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,25 +8325,25 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.04098436695841654</v>
+        <v>0.05080159321179373</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01539176755738058</v>
+        <v>-0.01473747998767071</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.001885433809501707</v>
+        <v>-0.02429197959876679</v>
       </c>
       <c r="FR14" t="n">
         <v>-0</v>
@@ -8352,43 +8352,43 @@
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.001371597360001756</v>
+        <v>0.001270735534074168</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.01834722825024067</v>
+        <v>-0.01930960078890075</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.02459857039447088</v>
+        <v>-0.03987122832901713</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.02231485745684398</v>
+        <v>0.02479059824193582</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>0</v>
